--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/WYOMING_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/WYOMING_2020.xlsx
@@ -726,7 +726,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Guerero</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="C21">
@@ -888,7 +888,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Praxedis G. Guerero</t>
+          <t>Praxedis G. Guerrero</t>
         </is>
       </c>
       <c r="C30">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C59">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C70">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C153">
